--- a/engagement_survey_forms/001_team_productivity_barriers_survey--engagement_survey_forms.xlsx
+++ b/engagement_survey_forms/001_team_productivity_barriers_survey--engagement_survey_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="37" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'small'}</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Small'}</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'large'}</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Large'}</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'flexible'}</t>
+          <t>flexible</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Flexible'}</t>
+          <t>Flexible</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'inflexible'}</t>
+          <t>inflexible</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Inflexible'}</t>
+          <t>Inflexible</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'unpredictable'}</t>
+          <t>unpredictable</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Unpredictable'}</t>
+          <t>Unpredictable</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1546,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1563,12 +1563,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1580,12 +1580,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1597,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1631,12 +1631,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'ad_hoc'}</t>
+          <t>ad_hoc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Ad Hoc'}</t>
+          <t>Ad Hoc</t>
         </is>
       </c>
     </row>
@@ -1665,12 +1665,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1682,12 +1682,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1699,12 +1699,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1716,12 +1716,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1750,12 +1750,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1767,12 +1767,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1784,12 +1784,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1818,12 +1818,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1835,12 +1835,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1886,12 +1886,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1920,12 +1920,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1937,12 +1937,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1954,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -1971,12 +1971,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1988,12 +1988,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2005,12 +2005,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2022,12 +2022,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2073,12 +2073,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2107,12 +2107,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2158,12 +2158,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>{'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -2175,12 +2175,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>{'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{'label':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>{'label': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{'label':_'video_conference'}</t>
+          <t>video_conference</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>{'label': 'Video conference'}</t>
+          <t>Video conference</t>
         </is>
       </c>
     </row>
@@ -2226,12 +2226,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{'label':_'very_high'}</t>
+          <t>very_high</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>{'label': 'Very High'}</t>
+          <t>Very High</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2243,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>{'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2260,12 +2260,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>{'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2277,12 +2277,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>{'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2294,12 +2294,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{'label':_'microsoft_teams'}</t>
+          <t>microsoft_teams</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>{'label': 'Microsoft Teams'}</t>
+          <t>Microsoft Teams</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2311,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{'label':_'slack'}</t>
+          <t>slack</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>{'label': 'Slack'}</t>
+          <t>Slack</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{'label':_'trello'}</t>
+          <t>trello</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>{'label': 'Trello'}</t>
+          <t>Trello</t>
         </is>
       </c>
     </row>
@@ -2345,12 +2345,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
